--- a/peak_strength(1).xlsx
+++ b/peak_strength(1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\94914\Desktop\APP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ABAE8D7-CB1F-44D4-9CCC-A7F39FF21E47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86586F16-030E-4992-A78B-32EC961E34DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,13 +22,78 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
-    <t>sigma2</t>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>σ</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>sigma3</t>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>σ</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>sigma1</t>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>σ</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>3</t>
+    </r>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -36,7 +101,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -197,6 +262,29 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <vertAlign val="subscript"/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
@@ -640,18 +728,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1008,307 +1093,310 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.4">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="3" t="s">
+    </row>
+    <row r="2" spans="1:3" ht="15.4" x14ac:dyDescent="0.4">
+      <c r="A2" s="1">
+        <v>165</v>
+      </c>
+      <c r="B2" s="1">
         <v>0</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="15.4" x14ac:dyDescent="0.4">
-      <c r="A2" s="2">
-        <v>165</v>
-      </c>
-      <c r="B2" s="2">
+      <c r="C2" s="1">
         <v>0</v>
       </c>
-      <c r="C2" s="2">
+    </row>
+    <row r="3" spans="1:3" ht="15.4" x14ac:dyDescent="0.4">
+      <c r="A3" s="1">
+        <v>346</v>
+      </c>
+      <c r="B3" s="1">
+        <v>79</v>
+      </c>
+      <c r="C3" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15.4" x14ac:dyDescent="0.4">
-      <c r="A3" s="2">
-        <v>346</v>
-      </c>
-      <c r="B3" s="2">
-        <v>79</v>
-      </c>
-      <c r="C3" s="2">
+    <row r="4" spans="1:3" ht="15.4" x14ac:dyDescent="0.4">
+      <c r="A4" s="1">
+        <v>291</v>
+      </c>
+      <c r="B4" s="1">
+        <v>149</v>
+      </c>
+      <c r="C4" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="15.4" x14ac:dyDescent="0.4">
-      <c r="A4" s="2">
-        <v>291</v>
-      </c>
-      <c r="B4" s="2">
-        <v>149</v>
-      </c>
-      <c r="C4" s="2">
+    <row r="5" spans="1:3" ht="15.4" x14ac:dyDescent="0.4">
+      <c r="A5" s="1">
+        <v>347</v>
+      </c>
+      <c r="B5" s="1">
+        <v>197</v>
+      </c>
+      <c r="C5" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15.4" x14ac:dyDescent="0.4">
-      <c r="A5" s="2">
+    <row r="6" spans="1:3" ht="15.4" x14ac:dyDescent="0.4">
+      <c r="A6" s="1">
+        <v>267</v>
+      </c>
+      <c r="B6" s="1">
+        <v>229</v>
+      </c>
+      <c r="C6" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="15.4" x14ac:dyDescent="0.4">
+      <c r="A7" s="1">
+        <v>410</v>
+      </c>
+      <c r="B7" s="1">
+        <v>30</v>
+      </c>
+      <c r="C7" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="15.4" x14ac:dyDescent="0.4">
+      <c r="A8" s="1">
+        <v>479</v>
+      </c>
+      <c r="B8" s="1">
+        <v>60</v>
+      </c>
+      <c r="C8" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="15.4" x14ac:dyDescent="0.4">
+      <c r="A9" s="1">
+        <v>599</v>
+      </c>
+      <c r="B9" s="1">
+        <v>100</v>
+      </c>
+      <c r="C9" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="15.4" x14ac:dyDescent="0.4">
+      <c r="A10" s="1">
+        <v>652</v>
+      </c>
+      <c r="B10" s="1">
+        <v>200</v>
+      </c>
+      <c r="C10" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="15.4" x14ac:dyDescent="0.4">
+      <c r="A11" s="1">
+        <v>571</v>
+      </c>
+      <c r="B11" s="1">
+        <v>249</v>
+      </c>
+      <c r="C11" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="15.4" x14ac:dyDescent="0.4">
+      <c r="A12" s="1">
+        <v>637</v>
+      </c>
+      <c r="B12" s="1">
+        <v>298</v>
+      </c>
+      <c r="C12" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="15.4" x14ac:dyDescent="0.4">
+      <c r="A13" s="1">
+        <v>702</v>
+      </c>
+      <c r="B13" s="1">
+        <v>60</v>
+      </c>
+      <c r="C13" s="1">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="15.4" x14ac:dyDescent="0.4">
+      <c r="A14" s="1">
+        <v>750</v>
+      </c>
+      <c r="B14" s="1">
+        <v>88</v>
+      </c>
+      <c r="C14" s="1">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="15.4" x14ac:dyDescent="0.4">
+      <c r="A15" s="1">
+        <v>766</v>
+      </c>
+      <c r="B15" s="1">
+        <v>103</v>
+      </c>
+      <c r="C15" s="1">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="15.4" x14ac:dyDescent="0.4">
+      <c r="A16" s="1">
+        <v>745</v>
+      </c>
+      <c r="B16" s="1">
+        <v>155</v>
+      </c>
+      <c r="C16" s="1">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="15.4" x14ac:dyDescent="0.4">
+      <c r="A17" s="1">
+        <v>816</v>
+      </c>
+      <c r="B17" s="1">
+        <v>199</v>
+      </c>
+      <c r="C17" s="1">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="15.4" x14ac:dyDescent="0.4">
+      <c r="A18" s="1">
+        <v>888</v>
+      </c>
+      <c r="B18" s="1">
+        <v>249</v>
+      </c>
+      <c r="C18" s="1">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="15.4" x14ac:dyDescent="0.4">
+      <c r="A19" s="1">
+        <v>828</v>
+      </c>
+      <c r="B19" s="1">
+        <v>299</v>
+      </c>
+      <c r="C19" s="1">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="15.4" x14ac:dyDescent="0.4">
+      <c r="A20" s="1">
+        <v>887</v>
+      </c>
+      <c r="B20" s="1">
         <v>347</v>
       </c>
-      <c r="B5" s="2">
-        <v>197</v>
-      </c>
-      <c r="C5" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="15.4" x14ac:dyDescent="0.4">
-      <c r="A6" s="2">
-        <v>267</v>
-      </c>
-      <c r="B6" s="2">
-        <v>229</v>
-      </c>
-      <c r="C6" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="15.4" x14ac:dyDescent="0.4">
-      <c r="A7" s="2">
-        <v>410</v>
-      </c>
-      <c r="B7" s="2">
-        <v>30</v>
-      </c>
-      <c r="C7" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="15.4" x14ac:dyDescent="0.4">
-      <c r="A8" s="2">
-        <v>479</v>
-      </c>
-      <c r="B8" s="2">
+      <c r="C20" s="1">
         <v>60</v>
       </c>
-      <c r="C8" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="15.4" x14ac:dyDescent="0.4">
-      <c r="A9" s="2">
-        <v>599</v>
-      </c>
-      <c r="B9" s="2">
+    </row>
+    <row r="21" spans="1:4" ht="15.4" x14ac:dyDescent="0.4">
+      <c r="A21" s="1">
+        <v>954</v>
+      </c>
+      <c r="B21" s="1">
+        <v>399</v>
+      </c>
+      <c r="C21" s="1">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="15.4" x14ac:dyDescent="0.4">
+      <c r="A22" s="1">
+        <v>815</v>
+      </c>
+      <c r="B22" s="1">
+        <v>449</v>
+      </c>
+      <c r="C22" s="1">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="15.4" x14ac:dyDescent="0.4">
+      <c r="A23" s="1">
+        <v>868</v>
+      </c>
+      <c r="B23" s="1">
         <v>100</v>
       </c>
-      <c r="C9" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="15.4" x14ac:dyDescent="0.4">
-      <c r="A10" s="2">
-        <v>652</v>
-      </c>
-      <c r="B10" s="2">
-        <v>200</v>
-      </c>
-      <c r="C10" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="15.4" x14ac:dyDescent="0.4">
-      <c r="A11" s="2">
-        <v>571</v>
-      </c>
-      <c r="B11" s="2">
-        <v>249</v>
-      </c>
-      <c r="C11" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="15.4" x14ac:dyDescent="0.4">
-      <c r="A12" s="2">
-        <v>637</v>
-      </c>
-      <c r="B12" s="2">
-        <v>298</v>
-      </c>
-      <c r="C12" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="15.4" x14ac:dyDescent="0.4">
-      <c r="A13" s="2">
-        <v>702</v>
-      </c>
-      <c r="B13" s="2">
-        <v>60</v>
-      </c>
-      <c r="C13" s="2">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="15.4" x14ac:dyDescent="0.4">
-      <c r="A14" s="2">
-        <v>750</v>
-      </c>
-      <c r="B14" s="2">
-        <v>88</v>
-      </c>
-      <c r="C14" s="2">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="15.4" x14ac:dyDescent="0.4">
-      <c r="A15" s="2">
-        <v>766</v>
-      </c>
-      <c r="B15" s="2">
-        <v>103</v>
-      </c>
-      <c r="C15" s="2">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="15.4" x14ac:dyDescent="0.4">
-      <c r="A16" s="2">
-        <v>745</v>
-      </c>
-      <c r="B16" s="2">
-        <v>155</v>
-      </c>
-      <c r="C16" s="2">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="15.4" x14ac:dyDescent="0.4">
-      <c r="A17" s="2">
-        <v>816</v>
-      </c>
-      <c r="B17" s="2">
+      <c r="C23" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="15.4" x14ac:dyDescent="0.4">
+      <c r="A24" s="1">
+        <v>959</v>
+      </c>
+      <c r="B24" s="1">
+        <v>164</v>
+      </c>
+      <c r="C24" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="15.4" x14ac:dyDescent="0.4">
+      <c r="A25" s="1">
+        <v>1001</v>
+      </c>
+      <c r="B25" s="1">
         <v>199</v>
       </c>
-      <c r="C17" s="2">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="15.4" x14ac:dyDescent="0.4">
-      <c r="A18" s="2">
-        <v>888</v>
-      </c>
-      <c r="B18" s="2">
-        <v>249</v>
-      </c>
-      <c r="C18" s="2">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="15.4" x14ac:dyDescent="0.4">
-      <c r="A19" s="2">
-        <v>828</v>
-      </c>
-      <c r="B19" s="2">
-        <v>299</v>
-      </c>
-      <c r="C19" s="2">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="15.4" x14ac:dyDescent="0.4">
-      <c r="A20" s="2">
-        <v>887</v>
-      </c>
-      <c r="B20" s="2">
-        <v>347</v>
-      </c>
-      <c r="C20" s="2">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="15.4" x14ac:dyDescent="0.4">
-      <c r="A21" s="2">
-        <v>954</v>
-      </c>
-      <c r="B21" s="2">
-        <v>399</v>
-      </c>
-      <c r="C21" s="2">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="15.4" x14ac:dyDescent="0.4">
-      <c r="A22" s="2">
-        <v>815</v>
-      </c>
-      <c r="B22" s="2">
-        <v>449</v>
-      </c>
-      <c r="C22" s="2">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="15.4" x14ac:dyDescent="0.4">
-      <c r="A23" s="2">
-        <v>868</v>
-      </c>
-      <c r="B23" s="2">
+      <c r="C25" s="1">
         <v>100</v>
       </c>
-      <c r="C23" s="2">
+      <c r="D25" s="1"/>
+    </row>
+    <row r="26" spans="1:4" ht="15.4" x14ac:dyDescent="0.4">
+      <c r="A26" s="1">
+        <v>945</v>
+      </c>
+      <c r="B26" s="1">
+        <v>248</v>
+      </c>
+      <c r="C26" s="1">
         <v>100</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" ht="15.4" x14ac:dyDescent="0.4">
-      <c r="A24" s="2">
-        <v>959</v>
-      </c>
-      <c r="B24" s="2">
-        <v>164</v>
-      </c>
-      <c r="C24" s="2">
+      <c r="D26" s="1"/>
+    </row>
+    <row r="27" spans="1:4" ht="15.4" x14ac:dyDescent="0.4">
+      <c r="A27" s="1">
+        <v>892</v>
+      </c>
+      <c r="B27" s="1">
+        <v>269</v>
+      </c>
+      <c r="C27" s="1">
         <v>100</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" ht="15.4" x14ac:dyDescent="0.4">
-      <c r="A25" s="2">
-        <v>1001</v>
-      </c>
-      <c r="B25" s="2">
-        <v>199</v>
-      </c>
-      <c r="C25" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="15.4" x14ac:dyDescent="0.4">
-      <c r="A26" s="2">
-        <v>945</v>
-      </c>
-      <c r="B26" s="2">
-        <v>248</v>
-      </c>
-      <c r="C26" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="15.4" x14ac:dyDescent="0.4">
-      <c r="A27" s="2">
-        <v>892</v>
-      </c>
-      <c r="B27" s="2">
-        <v>269</v>
-      </c>
-      <c r="C27" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" ht="15.4" x14ac:dyDescent="0.4">
+      <c r="D27" s="1"/>
+    </row>
+    <row r="28" spans="1:4" ht="15.4" x14ac:dyDescent="0.4">
       <c r="A28" s="1">
         <v>1048</v>
       </c>
@@ -1318,8 +1406,9 @@
       <c r="C28" s="1">
         <v>100</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" ht="15.4" x14ac:dyDescent="0.4">
+      <c r="D28" s="1"/>
+    </row>
+    <row r="29" spans="1:4" ht="15.4" x14ac:dyDescent="0.4">
       <c r="A29" s="1">
         <v>1058</v>
       </c>
@@ -1329,8 +1418,9 @@
       <c r="C29" s="1">
         <v>100</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" ht="15.4" x14ac:dyDescent="0.4">
+      <c r="D29" s="1"/>
+    </row>
+    <row r="30" spans="1:4" ht="15.4" x14ac:dyDescent="0.4">
       <c r="A30" s="1">
         <v>1155</v>
       </c>
@@ -1340,8 +1430,9 @@
       <c r="C30" s="1">
         <v>100</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" ht="15.4" x14ac:dyDescent="0.4">
+      <c r="D30" s="1"/>
+    </row>
+    <row r="31" spans="1:4" ht="15.4" x14ac:dyDescent="0.4">
       <c r="A31" s="1">
         <v>1118</v>
       </c>
@@ -1351,116 +1442,122 @@
       <c r="C31" s="1">
         <v>100</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A32">
+      <c r="D31" s="1"/>
+    </row>
+    <row r="32" spans="1:4" ht="15.4" x14ac:dyDescent="0.4">
+      <c r="A32" s="1">
         <v>1147</v>
       </c>
-      <c r="B32">
+      <c r="B32" s="1">
         <v>150</v>
       </c>
-      <c r="C32">
+      <c r="C32" s="1">
         <v>150</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A33">
+    <row r="33" spans="1:3" ht="15.4" x14ac:dyDescent="0.4">
+      <c r="A33" s="1">
         <v>1065</v>
       </c>
-      <c r="B33">
+      <c r="B33" s="1">
         <v>198</v>
       </c>
-      <c r="C33">
+      <c r="C33" s="1">
         <v>150</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A34">
+    <row r="34" spans="1:3" ht="15.4" x14ac:dyDescent="0.4">
+      <c r="A34" s="1">
         <v>1112</v>
       </c>
-      <c r="B34">
+      <c r="B34" s="1">
         <v>199</v>
       </c>
-      <c r="C34">
+      <c r="C34" s="1">
         <v>150</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A35">
+    <row r="35" spans="1:3" ht="15.4" x14ac:dyDescent="0.4">
+      <c r="A35" s="1">
         <v>1176</v>
       </c>
-      <c r="B35">
+      <c r="B35" s="1">
         <v>249</v>
       </c>
-      <c r="C35">
+      <c r="C35" s="1">
         <v>150</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A36">
+    <row r="36" spans="1:3" ht="15.4" x14ac:dyDescent="0.4">
+      <c r="A36" s="1">
         <v>1431</v>
       </c>
-      <c r="B36">
+      <c r="B36" s="1">
         <v>298</v>
       </c>
-      <c r="C36">
+      <c r="C36" s="1">
         <v>150</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A37">
+    <row r="37" spans="1:3" ht="15.4" x14ac:dyDescent="0.4">
+      <c r="A37" s="1">
         <v>1326</v>
       </c>
-      <c r="B37">
+      <c r="B37" s="1">
         <v>348</v>
       </c>
-      <c r="C37">
+      <c r="C37" s="1">
         <v>150</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A38">
+    <row r="38" spans="1:3" ht="15.4" x14ac:dyDescent="0.4">
+      <c r="A38" s="1">
         <v>1169</v>
       </c>
-      <c r="B38">
+      <c r="B38" s="1">
         <v>399</v>
       </c>
-      <c r="C38">
+      <c r="C38" s="1">
         <v>150</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A39">
+    <row r="39" spans="1:3" ht="15.4" x14ac:dyDescent="0.4">
+      <c r="A39" s="1">
         <v>1284</v>
       </c>
-      <c r="B39">
+      <c r="B39" s="1">
         <v>448</v>
       </c>
-      <c r="C39">
+      <c r="C39" s="1">
         <v>150</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A40">
+    <row r="40" spans="1:3" ht="15.4" x14ac:dyDescent="0.4">
+      <c r="A40" s="1">
         <v>1265</v>
       </c>
-      <c r="B40">
+      <c r="B40" s="1">
         <v>498</v>
       </c>
-      <c r="C40">
+      <c r="C40" s="1">
         <v>150</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A41">
+    <row r="41" spans="1:3" ht="15.4" x14ac:dyDescent="0.4">
+      <c r="A41" s="1">
         <v>1262</v>
       </c>
-      <c r="B41">
+      <c r="B41" s="1">
         <v>642</v>
       </c>
-      <c r="C41">
+      <c r="C41" s="1">
         <v>150</v>
       </c>
+    </row>
+    <row r="42" spans="1:3" ht="15.4" x14ac:dyDescent="0.4">
+      <c r="A42" s="1"/>
+      <c r="B42" s="1"/>
+      <c r="C42" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>

--- a/peak_strength(1).xlsx
+++ b/peak_strength(1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\94914\Desktop\APP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86586F16-030E-4992-A78B-32EC961E34DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{781FA417-8AB1-4B6D-9C8D-7104857D99BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1093,7 +1093,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.4">
@@ -1272,7 +1272,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="15.4" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:3" ht="15.4" x14ac:dyDescent="0.4">
       <c r="A17" s="1">
         <v>816</v>
       </c>
@@ -1283,7 +1283,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="15.4" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:3" ht="15.4" x14ac:dyDescent="0.4">
       <c r="A18" s="1">
         <v>888</v>
       </c>
@@ -1294,7 +1294,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="15.4" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:3" ht="15.4" x14ac:dyDescent="0.4">
       <c r="A19" s="1">
         <v>828</v>
       </c>
@@ -1305,7 +1305,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="15.4" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:3" ht="15.4" x14ac:dyDescent="0.4">
       <c r="A20" s="1">
         <v>887</v>
       </c>
@@ -1316,7 +1316,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="15.4" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:3" ht="15.4" x14ac:dyDescent="0.4">
       <c r="A21" s="1">
         <v>954</v>
       </c>
@@ -1327,7 +1327,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="15.4" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:3" ht="15.4" x14ac:dyDescent="0.4">
       <c r="A22" s="1">
         <v>815</v>
       </c>
@@ -1338,7 +1338,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="15.4" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:3" ht="15.4" x14ac:dyDescent="0.4">
       <c r="A23" s="1">
         <v>868</v>
       </c>
@@ -1349,7 +1349,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="15.4" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:3" ht="15.4" x14ac:dyDescent="0.4">
       <c r="A24" s="1">
         <v>959</v>
       </c>
@@ -1360,7 +1360,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="15.4" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:3" ht="15.4" x14ac:dyDescent="0.4">
       <c r="A25" s="1">
         <v>1001</v>
       </c>
@@ -1370,9 +1370,8 @@
       <c r="C25" s="1">
         <v>100</v>
       </c>
-      <c r="D25" s="1"/>
-    </row>
-    <row r="26" spans="1:4" ht="15.4" x14ac:dyDescent="0.4">
+    </row>
+    <row r="26" spans="1:3" ht="15.4" x14ac:dyDescent="0.4">
       <c r="A26" s="1">
         <v>945</v>
       </c>
@@ -1382,9 +1381,8 @@
       <c r="C26" s="1">
         <v>100</v>
       </c>
-      <c r="D26" s="1"/>
-    </row>
-    <row r="27" spans="1:4" ht="15.4" x14ac:dyDescent="0.4">
+    </row>
+    <row r="27" spans="1:3" ht="15.4" x14ac:dyDescent="0.4">
       <c r="A27" s="1">
         <v>892</v>
       </c>
@@ -1394,9 +1392,8 @@
       <c r="C27" s="1">
         <v>100</v>
       </c>
-      <c r="D27" s="1"/>
-    </row>
-    <row r="28" spans="1:4" ht="15.4" x14ac:dyDescent="0.4">
+    </row>
+    <row r="28" spans="1:3" ht="15.4" x14ac:dyDescent="0.4">
       <c r="A28" s="1">
         <v>1048</v>
       </c>
@@ -1406,9 +1403,8 @@
       <c r="C28" s="1">
         <v>100</v>
       </c>
-      <c r="D28" s="1"/>
-    </row>
-    <row r="29" spans="1:4" ht="15.4" x14ac:dyDescent="0.4">
+    </row>
+    <row r="29" spans="1:3" ht="15.4" x14ac:dyDescent="0.4">
       <c r="A29" s="1">
         <v>1058</v>
       </c>
@@ -1418,9 +1414,8 @@
       <c r="C29" s="1">
         <v>100</v>
       </c>
-      <c r="D29" s="1"/>
-    </row>
-    <row r="30" spans="1:4" ht="15.4" x14ac:dyDescent="0.4">
+    </row>
+    <row r="30" spans="1:3" ht="15.4" x14ac:dyDescent="0.4">
       <c r="A30" s="1">
         <v>1155</v>
       </c>
@@ -1430,9 +1425,8 @@
       <c r="C30" s="1">
         <v>100</v>
       </c>
-      <c r="D30" s="1"/>
-    </row>
-    <row r="31" spans="1:4" ht="15.4" x14ac:dyDescent="0.4">
+    </row>
+    <row r="31" spans="1:3" ht="15.4" x14ac:dyDescent="0.4">
       <c r="A31" s="1">
         <v>1118</v>
       </c>
@@ -1442,9 +1436,8 @@
       <c r="C31" s="1">
         <v>100</v>
       </c>
-      <c r="D31" s="1"/>
-    </row>
-    <row r="32" spans="1:4" ht="15.4" x14ac:dyDescent="0.4">
+    </row>
+    <row r="32" spans="1:3" ht="15.4" x14ac:dyDescent="0.4">
       <c r="A32" s="1">
         <v>1147</v>
       </c>
